--- a/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffTable.xlsx
+++ b/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffTable.xlsx
@@ -950,12 +950,9 @@
   </sheetPr>
   <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>stackBehavior</t>
         </is>

--- a/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffTable.xlsx
+++ b/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffTable.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -929,6 +929,44 @@
       <c r="H13" s="3" t="inlineStr">
         <is>
           <t>필드 존용. 존이 직접 제거하므로 duration은 0이어야 함</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>buff.fighter_awakening</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>각성</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>일정 시간 전투 능력이 크게 향상됩니다.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>attackPowerPercent:30;attackSpeedPercent:25;moveSpeedPercent:15;defensePowerPercent:30</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>RefreshDuration</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>파이터 궁극기(각성) 전용</t>
         </is>
       </c>
     </row>

--- a/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffTable.xlsx
+++ b/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffTable.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -967,6 +967,120 @@
       <c r="H14" t="inlineStr">
         <is>
           <t>파이터 궁극기(각성) 전용</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>buff.fighter_awakening_evo1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>가속 각성</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>일정 시간 동안 공격 속도와 일반공격 피해가 크게 증가합니다.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>attackSpeedPercent:50;normalDamagePercent:50;attackPowerPercent:15;moveSpeedPercent:15;defensePowerPercent:30</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>15</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>RefreshDuration</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>파이터 궁극기(각성) 진화1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>buff.fighter_awakening_evo2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>연산 각성</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>일정 시간 동안 스킬 재사용 대기시간이 줄고 스킬 피해가 크게 증가합니다.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>cdrFlat:25;skillDamagePercent:50;attackPowerPercent:15;moveSpeedPercent:15;defensePowerPercent:30</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>15</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>RefreshDuration</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>파이터 궁극기(각성) 진화2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>buff.fighter_awakening_evo3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>과부하 각성</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>짧은 시간 동안 능력치가 크게 증가합니다.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>attackPowerPercent:30;attackSpeedPercent:25;moveSpeedPercent:15;defensePowerPercent:30</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>RefreshDuration</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>파이터 궁극기(각성) 진화3 - 지속시간 단축</t>
         </is>
       </c>
     </row>

--- a/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffTable.xlsx
+++ b/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffTable.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1081,6 +1081,82 @@
       <c r="H17" t="inlineStr">
         <is>
           <t>파이터 궁극기(각성) 진화3 - 지속시간 단축</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>buff.gunner_bombard_evo1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>제압 폭격</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>일정 시간 동안 공격 속도와 일반공격 피해가 크게 증가합니다.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>attackSpeedPercent:50;normalDamagePercent:50</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>15</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>RefreshDuration</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>거너 궁극기(융단폭격) 진화1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>buff.gunner_bombard_evo2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>화력 관제</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>일정 시간 동안 스킬 재사용 대기시간이 줄고 스킬 피해가 크게 증가합니다.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>cdrFlat:25;skillDamagePercent:50</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>15</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>RefreshDuration</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>거너 궁극기(융단폭격) 진화2</t>
         </is>
       </c>
     </row>

--- a/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffTable.xlsx
+++ b/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffTable.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1081,82 +1081,6 @@
       <c r="H17" t="inlineStr">
         <is>
           <t>파이터 궁극기(각성) 진화3 - 지속시간 단축</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>buff.gunner_bombard_evo1</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>제압 폭격</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>일정 시간 동안 공격 속도와 일반공격 피해가 크게 증가합니다.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>attackSpeedPercent:50;normalDamagePercent:50</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>15</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>RefreshDuration</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>거너 궁극기(융단폭격) 진화1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>buff.gunner_bombard_evo2</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>화력 관제</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>일정 시간 동안 스킬 재사용 대기시간이 줄고 스킬 피해가 크게 증가합니다.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>cdrFlat:25;skillDamagePercent:50</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>15</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>RefreshDuration</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>거너 궁극기(융단폭격) 진화2</t>
         </is>
       </c>
     </row>
